--- a/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:19</t>
+          <t>2026-09-09 00:51:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:20</t>
+          <t>2026-09-09 00:51:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:21</t>
+          <t>2026-09-09 00:51:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:23</t>
+          <t>2026-09-09 00:51:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:23</t>
+          <t>2026-09-09 00:51:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:23</t>
+          <t>2026-09-09 00:51:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:23</t>
+          <t>2026-09-09 00:51:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:23</t>
+          <t>2026-09-09 00:51:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:28</t>
+          <t>2026-09-09 01:17:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:29</t>
+          <t>2026-09-09 01:17:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:31</t>
+          <t>2026-09-09 01:17:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:32</t>
+          <t>2026-09-09 01:17:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:32</t>
+          <t>2026-09-09 01:17:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:32</t>
+          <t>2026-09-09 01:17:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:32</t>
+          <t>2026-09-09 01:17:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:32</t>
+          <t>2026-09-09 01:17:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.22%480,000</t>
+          <t>8.06%480,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.22%</t>
+          <t>8.06%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5960</v>
+        <v>5925</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.89%364,000</t>
+          <t>7.83%364,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.89%</t>
+          <t>7.83%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5795</v>
+        <v>5615</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.81%323,000</t>
+          <t>6.58%323,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3285</v>
+        <v>993</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.59%468,000</t>
+          <t>6.20%1,720,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>6.20%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>468000</v>
+        <v>1720000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>954</v>
+        <v>3380</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.45%1,570,000</t>
+          <t>5.74%468,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1570000</v>
+        <v>468000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5550</v>
+        <v>5760</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.25%260,000</t>
+          <t>5.43%260,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1935</v>
+        <v>1975</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.68%665,000</t>
+          <t>4.77%665,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.77%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.02%1075</t>
+          <t>+2.33%1100</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.41%1,127,000</t>
+          <t>4.50%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.12%212,000</t>
+          <t>4.14%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19220</v>
+        <v>2015</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.80%54,300</t>
+          <t>3.87%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>54300</v>
+        <v>529000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1955</v>
+        <v>18605</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.76%529,000</t>
+          <t>3.67%54,300</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>529000</v>
+        <v>54300</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.32%3620</t>
+          <t>+7.3%999</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3620</v>
+        <v>999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.23%245,000</t>
+          <t>3.44%950,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>245000</v>
+        <v>950000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+6.17%6970</t>
+          <t>-0.28%3610</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+6.17%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6970</v>
+        <v>3610</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.04%120,000</t>
+          <t>3.21%245,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>120000</v>
+        <v>245000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1025</v>
+        <v>1110</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.76%739,000</t>
+          <t>2.98%739,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:29</t>
+          <t>2026-09-09 19:34:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.02%931</t>
+          <t>-3.59%6720</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>931</v>
+        <v>6720</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.54%750,000</t>
+          <t>2.93%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>750000</v>
+        <v>120000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4991環宇-KY</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.2%493</t>
+          <t>+6.5%2295</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>493</v>
+        <v>2295</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.15%1,200,000</t>
+          <t>2.26%271,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1200000</v>
+        <v>271000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>4991環宇-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.86%2155</t>
+          <t>+1.22%499</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2155</v>
+        <v>499</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.12%271,000</t>
+          <t>2.17%1,200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>271000</v>
+        <v>1200000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.91%42,000</t>
+          <t>1.89%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.65%158,400</t>
+          <t>1.64%158,400</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>7734印能科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>+2.41%2980</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2470</v>
+        <v>2980</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.61%179,000</t>
+          <t>1.62%150,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>179000</v>
+        <v>150000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,34 +1724,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7734印能科技</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.17%2910</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2910</v>
+        <v>2465</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.59%150,000</t>
+          <t>1.60%179,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>150000</v>
+        <v>179000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.50%306,000</t>
+          <t>1.49%306,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.13%2635</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2635</v>
+        <v>1345</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.46%152,000</t>
+          <t>1.38%282,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>152000</v>
+        <v>282000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.27%149,139</t>
+          <t>1.26%149,139</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,34 +1968,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>-1.33%520</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1225</v>
+        <v>520</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.26%282,000</t>
+          <t>1.23%650,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>282000</v>
+        <v>650000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-9.91%527</t>
+          <t>-3.04%2555</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.91%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>527</v>
+        <v>2555</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.25%650,000</t>
+          <t>1.22%132,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>650000</v>
+        <v>132000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.09%1385</t>
+          <t>+2.65%193.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1385</v>
+        <v>193.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.00%198,000</t>
+          <t>0.98%1,400,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>198000</v>
+        <v>1400000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-3.33%188.5</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>188.5</v>
+        <v>1330</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.96%1,400,000</t>
+          <t>0.96%198,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1400000</v>
+        <v>198000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+10%7700</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7700</v>
+        <v>1795</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.64%23,000</t>
+          <t>0.61%94,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>23000</v>
+        <v>94000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:30</t>
+          <t>2026-09-09 19:34:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-5.45%7280</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1805</v>
+        <v>7280</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.62%94,000</t>
+          <t>0.61%23,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>94000</v>
+        <v>23000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>6831邁科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.2%907</t>
+          <t>+2.68%575</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>907</v>
+        <v>575</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.55%168,000</t>
+          <t>0.52%250,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>168000</v>
+        <v>250000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6831邁科</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.41%560</t>
+          <t>0%955</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>560</v>
+        <v>955</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.51%250,000</t>
+          <t>0.38%110,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>250000</v>
+        <v>110000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.65%955</t>
+          <t>0%643</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>955</v>
+        <v>643</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.38%110,000</t>
+          <t>0.34%146,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>110000</v>
+        <v>146000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.46%236</t>
+          <t>-1.06%233.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>236</v>
+        <v>233.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>4749新應材</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.16%643</t>
+          <t>-1.28%770</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>643</v>
+        <v>770</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.34%146,000</t>
+          <t>0.27%95,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>146000</v>
+        <v>95000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4749新應材</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.89%780</t>
+          <t>+3.29%157</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>780</v>
+        <v>157</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.27%95,000</t>
+          <t>0.12%211,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>95000</v>
+        <v>211000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>4576大銀微系統</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.56%152</t>
+          <t>+3.61%244</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>+3.61%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.12%211,000</t>
+          <t>0.06%72,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>211000</v>
+        <v>72000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4576大銀微系統</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-4.66%235.5</t>
+          <t>+0.56%270</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.66%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>235.5</v>
+        <v>270</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.06%72,000</t>
+          <t>0.04%42,650</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>72000</v>
+        <v>42650</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.65%268.5</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>268.5</v>
+        <v>141.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.04%42,650</t>
+          <t>0.04%78,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>42650</v>
+        <v>78000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3163波若威</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>-0.28%724</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>137</v>
+        <v>724</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.04%78,000</t>
+          <t>0.03%13,300</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>78000</v>
+        <v>13300</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3163波若威</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-3.46%726</t>
+          <t>+3.56%233</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>726</v>
+        <v>233</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.04%13,300</t>
+          <t>0.03%34,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>13300</v>
+        <v>34000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.88%225</t>
+          <t>-1.67%442.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>225</v>
+        <v>442.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.03%34,000</t>
+          <t>0.02%10,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>34000</v>
+        <v>10000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,34 +3066,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.6%450</t>
+          <t>-3.1%3905</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>450</v>
+        <v>3905</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.02%10,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.25%4030</t>
+          <t>-0.61%653</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4030</v>
+        <v>653</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:17:31</t>
+          <t>2026-09-09 19:34:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,346 +3188,41 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-3.38%657</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.38%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>&lt;0.01%3,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-09-09 01:17:33</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-0.48%618</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-0.48%</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>618</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>&lt;0.01%3,000</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-09-09 01:17:33</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>3533嘉澤</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-4.42%1620</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-4.42%</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>1620</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>&lt;0.01%1,000</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-09-09 01:17:33</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>3491昇達科</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-1.32%1490</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-1.32%</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>1490</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>&lt;0.01%1,000</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-09-09 01:17:33</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1590亞德客-KY</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-2.55%1335</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-2.55%</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>1335</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>&lt;0.01%1,000</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-09 01:17:33</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>8028昇陽半導體</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-5.21%236.5</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-5.21%</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>236.5</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>&lt;0.01%1,000</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:10</t>
+          <t>2026-09-09 22:37:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:11</t>
+          <t>2026-09-09 22:37:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:12</t>
+          <t>2026-09-09 22:37:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:34</t>
+          <t>2026-09-09 22:49:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:35</t>
+          <t>2026-09-09 22:49:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:36</t>
+          <t>2026-09-09 22:49:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:27</t>
+          <t>2026-09-09 23:10:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:29</t>
+          <t>2026-09-09 23:10:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:30</t>
+          <t>2026-09-09 23:10:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
